--- a/artfynd/S 3630-2024 artfynd.xlsx
+++ b/artfynd/S 3630-2024 artfynd.xlsx
@@ -3167,7 +3167,7 @@
         <v>136326066</v>
       </c>
       <c r="B25" t="n">
-        <v>106517</v>
+        <v>106520</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>136326057</v>
       </c>
       <c r="B26" t="n">
-        <v>107859</v>
+        <v>107862</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 3630-2024 artfynd.xlsx
+++ b/artfynd/S 3630-2024 artfynd.xlsx
@@ -3167,7 +3167,7 @@
         <v>136326066</v>
       </c>
       <c r="B25" t="n">
-        <v>106520</v>
+        <v>106521</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>136326057</v>
       </c>
       <c r="B26" t="n">
-        <v>107862</v>
+        <v>107863</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 3630-2024 artfynd.xlsx
+++ b/artfynd/S 3630-2024 artfynd.xlsx
@@ -3167,7 +3167,7 @@
         <v>136326066</v>
       </c>
       <c r="B25" t="n">
-        <v>106521</v>
+        <v>106526</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>136326057</v>
       </c>
       <c r="B26" t="n">
-        <v>107863</v>
+        <v>107868</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 3630-2024 artfynd.xlsx
+++ b/artfynd/S 3630-2024 artfynd.xlsx
@@ -3167,7 +3167,7 @@
         <v>136326066</v>
       </c>
       <c r="B25" t="n">
-        <v>106526</v>
+        <v>106528</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>136326057</v>
       </c>
       <c r="B26" t="n">
-        <v>107868</v>
+        <v>107870</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 3630-2024 artfynd.xlsx
+++ b/artfynd/S 3630-2024 artfynd.xlsx
@@ -3167,7 +3167,7 @@
         <v>136326066</v>
       </c>
       <c r="B25" t="n">
-        <v>106528</v>
+        <v>106534</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>136326057</v>
       </c>
       <c r="B26" t="n">
-        <v>107870</v>
+        <v>107876</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
